--- a/exports/TITAN_full_report.xlsx
+++ b/exports/TITAN_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q67"/>
+  <dimension ref="A1:U67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>6.85</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44582.55208333334</v>
+        <v>44585.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>2525</v>
+        <v>2418.45</v>
       </c>
       <c r="I2" t="n">
         <v>2522.229473</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K2" t="n">
-        <v>-4.3</v>
+        <v>-8.34</v>
       </c>
       <c r="L2" t="n">
-        <v>5.06</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="M2" t="n">
         <v>0.74</v>
       </c>
       <c r="N2" t="n">
-        <v>1.64</v>
+        <v>4.83</v>
       </c>
       <c r="O2" t="n">
         <v>3.21</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>7.94</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44594.55208333334</v>
+        <v>44595.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>2468</v>
+        <v>2479</v>
       </c>
       <c r="I3" t="n">
         <v>2471.984471702296</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K3" t="n">
-        <v>-2.05</v>
+        <v>-2.5</v>
       </c>
       <c r="L3" t="n">
         <v>4.26</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>6.26</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44624.38541666666</v>
+        <v>44624.55208333334</v>
       </c>
       <c r="H4" t="n">
-        <v>2493.35</v>
+        <v>2441</v>
       </c>
       <c r="I4" t="n">
         <v>2461.004788824843</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>29</v>
+        <v>29.16666666666667</v>
       </c>
       <c r="K4" t="n">
-        <v>0.58</v>
+        <v>-1.53</v>
       </c>
       <c r="L4" t="n">
         <v>5.04</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>8.44</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44635.55208333334</v>
+        <v>44636.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>2550.8</v>
+        <v>2580.1</v>
       </c>
       <c r="I5" t="n">
         <v>2556.118637509923</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>11</v>
+        <v>11.83333333333333</v>
       </c>
       <c r="K5" t="n">
-        <v>-4.5</v>
+        <v>-5.7</v>
       </c>
       <c r="L5" t="n">
-        <v>5.65</v>
+        <v>6.23</v>
       </c>
       <c r="M5" t="n">
         <v>2.59</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -762,28 +833,28 @@
         <v>5.41</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44644.55208333334</v>
+        <v>44645.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>2619</v>
+        <v>2534.55</v>
       </c>
       <c r="I6" t="n">
         <v>2587.251158942684</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K6" t="n">
-        <v>1.51</v>
+        <v>-1.77</v>
       </c>
       <c r="L6" t="n">
-        <v>0.55</v>
+        <v>2.14</v>
       </c>
       <c r="M6" t="n">
         <v>0.02</v>
       </c>
       <c r="N6" t="n">
-        <v>2.53</v>
+        <v>3.4</v>
       </c>
       <c r="O6" t="n">
         <v>1.43</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>8.289999999999999</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44698.38541666666</v>
+        <v>44698.55208333334</v>
       </c>
       <c r="H7" t="n">
-        <v>2148.45</v>
+        <v>2181</v>
       </c>
       <c r="I7" t="n">
         <v>2179.713323759997</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>53</v>
+        <v>53.16666666666666</v>
       </c>
       <c r="K7" t="n">
-        <v>15.23</v>
+        <v>13.95</v>
       </c>
       <c r="L7" t="n">
         <v>3.92</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>7.48</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44718.55208333334</v>
+        <v>44719.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>2198</v>
+        <v>2101.5</v>
       </c>
       <c r="I8" t="n">
         <v>2125.469370012129</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>20</v>
+        <v>20.83333333333333</v>
       </c>
       <c r="K8" t="n">
-        <v>0.78</v>
+        <v>-3.65</v>
       </c>
       <c r="L8" t="n">
         <v>4.84</v>
@@ -897,7 +992,7 @@
         <v>2.1</v>
       </c>
       <c r="N8" t="n">
-        <v>4.38</v>
+        <v>4.46</v>
       </c>
       <c r="O8" t="n">
         <v>3.32</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>8.619999999999999</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44747.55208333334</v>
+        <v>44748.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>1958</v>
+        <v>2013.9</v>
       </c>
       <c r="I9" t="n">
         <v>2010.553635498927</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K9" t="n">
-        <v>6.83</v>
+        <v>4.17</v>
       </c>
       <c r="L9" t="n">
         <v>3.43</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>8.33</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44831.55208333334</v>
+        <v>44832.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>2604.95</v>
+        <v>2594.25</v>
       </c>
       <c r="I10" t="n">
         <v>2603.998327932581</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>83.16666666666667</v>
+        <v>84</v>
       </c>
       <c r="K10" t="n">
-        <v>29.35</v>
+        <v>28.82</v>
       </c>
       <c r="L10" t="n">
         <v>3.59</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>114</v>
+        <v>115</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -1047,28 +1178,28 @@
         <v>6.22</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44840.55208333334</v>
+        <v>44841.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>2588</v>
+        <v>2721.8</v>
       </c>
       <c r="I11" t="n">
         <v>2689.335373714071</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K11" t="n">
-        <v>0.24</v>
+        <v>-4.92</v>
       </c>
       <c r="L11" t="n">
-        <v>1.66</v>
+        <v>5.81</v>
       </c>
       <c r="M11" t="n">
-        <v>2.01</v>
+        <v>3.94</v>
       </c>
       <c r="N11" t="n">
-        <v>2.69</v>
+        <v>5.47</v>
       </c>
       <c r="O11" t="n">
         <v>-1.27</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>6.6</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44874.55208333334</v>
+        <v>44875.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>2711.95</v>
+        <v>2639.9</v>
       </c>
       <c r="I12" t="n">
         <v>2649.518040434127</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>33.16666666666666</v>
+        <v>34</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.36</v>
+        <v>-3.01</v>
       </c>
       <c r="L12" t="n">
         <v>5.16</v>
@@ -1125,7 +1268,7 @@
         <v>1.06</v>
       </c>
       <c r="N12" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="O12" t="n">
         <v>5.47</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>6</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44895.38541666666</v>
+        <v>44895.55208333334</v>
       </c>
       <c r="H13" t="n">
-        <v>2625</v>
+        <v>2657.25</v>
       </c>
       <c r="I13" t="n">
         <v>2656.50201317256</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>20</v>
+        <v>20.16666666666667</v>
       </c>
       <c r="K13" t="n">
-        <v>0.5600000000000001</v>
+        <v>-0.66</v>
       </c>
       <c r="L13" t="n">
         <v>2.7</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,28 +1385,28 @@
         <v>3.92</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44909.55208333334</v>
+        <v>44910.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>2592</v>
+        <v>2545.6</v>
       </c>
       <c r="I14" t="n">
         <v>2560.859149978929</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>14</v>
+        <v>14.83333333333333</v>
       </c>
       <c r="K14" t="n">
-        <v>-2.46</v>
+        <v>-4.2</v>
       </c>
       <c r="L14" t="n">
-        <v>3.47</v>
+        <v>4.33</v>
       </c>
       <c r="M14" t="n">
-        <v>0.02</v>
+        <v>0.27</v>
       </c>
       <c r="N14" t="n">
-        <v>0.93</v>
+        <v>2.76</v>
       </c>
       <c r="O14" t="n">
         <v>1.73</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,28 +1454,28 @@
         <v>4.19</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44922.55208333334</v>
+        <v>44923.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>2502.9</v>
+        <v>2580.8</v>
       </c>
       <c r="I15" t="n">
         <v>2571.146708845021</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K15" t="n">
-        <v>1.68</v>
+        <v>-1.38</v>
       </c>
       <c r="L15" t="n">
-        <v>1.66</v>
+        <v>1.98</v>
       </c>
       <c r="M15" t="n">
         <v>0.32</v>
       </c>
       <c r="N15" t="n">
-        <v>1.59</v>
+        <v>2.8</v>
       </c>
       <c r="O15" t="n">
         <v>-2.76</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S15" t="b">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1332,28 +1523,28 @@
         <v>5.63</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44932.55208333334</v>
+        <v>44935.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>2537</v>
+        <v>2487.95</v>
       </c>
       <c r="I16" t="n">
         <v>2498.9591247413</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.7</v>
+        <v>-3.6</v>
       </c>
       <c r="L16" t="n">
-        <v>3.23</v>
+        <v>4.31</v>
       </c>
       <c r="M16" t="n">
         <v>0.7</v>
       </c>
       <c r="N16" t="n">
-        <v>1.14</v>
+        <v>1.85</v>
       </c>
       <c r="O16" t="n">
         <v>2.8</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>5.41</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44959.55208333334</v>
+        <v>44960.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>2325</v>
+        <v>2435.2</v>
       </c>
       <c r="I17" t="n">
         <v>2406.783311822469</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K17" t="n">
-        <v>6.55</v>
+        <v>2.12</v>
       </c>
       <c r="L17" t="n">
         <v>1.69</v>
@@ -1410,7 +1613,7 @@
         <v>2.93</v>
       </c>
       <c r="N17" t="n">
-        <v>0.58</v>
+        <v>5.73</v>
       </c>
       <c r="O17" t="n">
         <v>-1.85</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,28 +1661,28 @@
         <v>8.779999999999999</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44978.55208333334</v>
+        <v>44979.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>2466</v>
+        <v>2428.3</v>
       </c>
       <c r="I18" t="n">
         <v>2440.558474307174</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K18" t="n">
-        <v>1.26</v>
+        <v>-0.28</v>
       </c>
       <c r="L18" t="n">
         <v>4.73</v>
       </c>
       <c r="M18" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="N18" t="n">
-        <v>0.88</v>
+        <v>1.46</v>
       </c>
       <c r="O18" t="n">
         <v>5.73</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1503,28 +1730,28 @@
         <v>4.19</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45000.55208333334</v>
+        <v>45001.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>2400</v>
+        <v>2453.95</v>
       </c>
       <c r="I19" t="n">
         <v>2413.466253185696</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K19" t="n">
-        <v>1.17</v>
+        <v>-1.06</v>
       </c>
       <c r="L19" t="n">
-        <v>1.42</v>
+        <v>2.21</v>
       </c>
       <c r="M19" t="n">
         <v>0.8</v>
       </c>
       <c r="N19" t="n">
-        <v>1.69</v>
+        <v>2.08</v>
       </c>
       <c r="O19" t="n">
         <v>-1.46</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>4.62</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45064.55208333334</v>
+        <v>45065.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>2722</v>
+        <v>2701.6</v>
       </c>
       <c r="I20" t="n">
         <v>2720.050258091984</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>63.16666666666666</v>
+        <v>64</v>
       </c>
       <c r="K20" t="n">
-        <v>10.92</v>
+        <v>10.09</v>
       </c>
       <c r="L20" t="n">
         <v>1.67</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>3.02</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45075.38541666666</v>
+        <v>45075.55208333334</v>
       </c>
       <c r="H21" t="n">
-        <v>2773.55</v>
+        <v>2813.95</v>
       </c>
       <c r="I21" t="n">
         <v>2774.624956086285</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>10</v>
+        <v>10.16666666666667</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.66</v>
+        <v>-4.16</v>
       </c>
       <c r="L21" t="n">
-        <v>2.9</v>
+        <v>4.45</v>
       </c>
       <c r="M21" t="n">
         <v>0.18</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>4.22</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45114.55208333334</v>
+        <v>45117.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>3142.35</v>
+        <v>3051.7</v>
       </c>
       <c r="I22" t="n">
         <v>3054.953728918626</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>39</v>
+        <v>41.83333333333334</v>
       </c>
       <c r="K22" t="n">
-        <v>11.67</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="L22" t="n">
         <v>1.46</v>
@@ -1695,7 +1958,7 @@
         <v>0.27</v>
       </c>
       <c r="N22" t="n">
-        <v>1.21</v>
+        <v>2.88</v>
       </c>
       <c r="O22" t="n">
         <v>2.69</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>5.9</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45148.55208333334</v>
+        <v>45149.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>2988</v>
+        <v>3059.15</v>
       </c>
       <c r="I23" t="n">
         <v>3004.298660555593</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>31.16666666666667</v>
+        <v>32</v>
       </c>
       <c r="K23" t="n">
-        <v>2.09</v>
+        <v>-0.24</v>
       </c>
       <c r="L23" t="n">
         <v>3.38</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>5.1</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45196.38541666666</v>
+        <v>45196.55208333334</v>
       </c>
       <c r="H24" t="n">
-        <v>3234.95</v>
+        <v>3217.5</v>
       </c>
       <c r="I24" t="n">
         <v>3224.833946622645</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>47</v>
+        <v>47.16666666666666</v>
       </c>
       <c r="K24" t="n">
-        <v>5.75</v>
+        <v>5.18</v>
       </c>
       <c r="L24" t="n">
         <v>2.65</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>3.37</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45205.38541666666</v>
+        <v>45205.55208333334</v>
       </c>
       <c r="H25" t="n">
-        <v>3273</v>
+        <v>3307</v>
       </c>
       <c r="I25" t="n">
         <v>3273.251744745214</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>8.833333333333334</v>
+        <v>9</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.72</v>
+        <v>-2.78</v>
       </c>
       <c r="L25" t="n">
-        <v>1.94</v>
+        <v>3.18</v>
       </c>
       <c r="M25" t="n">
         <v>0.35</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,22 +2213,22 @@
         <v>4.24</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45222.55208333334</v>
+        <v>45224.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>3219.95</v>
+        <v>3198.1</v>
       </c>
       <c r="I26" t="n">
         <v>3218.352105166685</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>17</v>
+        <v>18.83333333333333</v>
       </c>
       <c r="K26" t="n">
-        <v>-2.63</v>
+        <v>-3.29</v>
       </c>
       <c r="L26" t="n">
-        <v>2.94</v>
+        <v>3.34</v>
       </c>
       <c r="M26" t="n">
         <v>0.42</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>3.89</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45232.55208333334</v>
+        <v>45233.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>3208.95</v>
+        <v>3257.4</v>
       </c>
       <c r="I27" t="n">
         <v>3213.380234078731</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.34</v>
+        <v>-1.85</v>
       </c>
       <c r="L27" t="n">
-        <v>1.19</v>
+        <v>2.06</v>
       </c>
       <c r="M27" t="n">
         <v>0.91</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>4.54</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45321.55208333334</v>
+        <v>45322.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>3749</v>
+        <v>3686.1</v>
       </c>
       <c r="I28" t="n">
         <v>3694.89714123393</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>88.16666666666667</v>
+        <v>89</v>
       </c>
       <c r="K28" t="n">
-        <v>15.09</v>
+        <v>13.16</v>
       </c>
       <c r="L28" t="n">
         <v>1.61</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>119</v>
+        <v>120</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>4</v>
+      </c>
+      <c r="U28" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>6.64</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45338.55208333334</v>
+        <v>45341.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>3648.65</v>
+        <v>3708</v>
       </c>
       <c r="I29" t="n">
         <v>3686.208180865822</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K29" t="n">
-        <v>1.02</v>
+        <v>-0.59</v>
       </c>
       <c r="L29" t="n">
         <v>2.41</v>
@@ -2094,7 +2441,7 @@
         <v>1.1</v>
       </c>
       <c r="N29" t="n">
-        <v>0.98</v>
+        <v>1.33</v>
       </c>
       <c r="O29" t="n">
         <v>-1.38</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>4.92</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45363.55208333334</v>
+        <v>45364.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>3753.2</v>
+        <v>3626.4</v>
       </c>
       <c r="I30" t="n">
         <v>3636.445016772997</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K30" t="n">
-        <v>1.22</v>
+        <v>-2.2</v>
       </c>
       <c r="L30" t="n">
         <v>4.12</v>
@@ -2151,7 +2510,7 @@
         <v>0.89</v>
       </c>
       <c r="N30" t="n">
-        <v>1.75</v>
+        <v>3.28</v>
       </c>
       <c r="O30" t="n">
         <v>1.33</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>6.48</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45377.55208333334</v>
+        <v>45378.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>3699.3</v>
+        <v>3723.55</v>
       </c>
       <c r="I31" t="n">
         <v>3716.281515394461</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K31" t="n">
-        <v>-2.01</v>
+        <v>-2.68</v>
       </c>
       <c r="L31" t="n">
         <v>3.74</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2244,28 +2627,28 @@
         <v>3.87</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45392.55208333334</v>
+        <v>45394.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>3709.95</v>
+        <v>3638.85</v>
       </c>
       <c r="I32" t="n">
         <v>3655.32857265821</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.37</v>
+        <v>-2.27</v>
       </c>
       <c r="L32" t="n">
-        <v>1.59</v>
+        <v>2.9</v>
       </c>
       <c r="M32" t="n">
-        <v>0.26</v>
+        <v>0.55</v>
       </c>
       <c r="N32" t="n">
-        <v>1.67</v>
+        <v>2.34</v>
       </c>
       <c r="O32" t="n">
         <v>1.59</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>4.51</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45434.55208333334</v>
+        <v>45435.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>3382.95</v>
+        <v>3432.3</v>
       </c>
       <c r="I33" t="n">
         <v>3408.231783557565</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>40.16666666666666</v>
+        <v>41</v>
       </c>
       <c r="K33" t="n">
-        <v>7.03</v>
+        <v>5.68</v>
       </c>
       <c r="L33" t="n">
         <v>1.54</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -2358,28 +2765,28 @@
         <v>4.41</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45441.55208333334</v>
+        <v>45442.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>3378</v>
+        <v>3296</v>
       </c>
       <c r="I34" t="n">
         <v>3317.842602241105</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K34" t="n">
-        <v>-1.58</v>
+        <v>-3.97</v>
       </c>
       <c r="L34" t="n">
-        <v>1.78</v>
+        <v>4.51</v>
       </c>
       <c r="M34" t="n">
-        <v>0.13</v>
+        <v>0.38</v>
       </c>
       <c r="N34" t="n">
-        <v>0.98</v>
+        <v>2.61</v>
       </c>
       <c r="O34" t="n">
         <v>1.82</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2415,28 +2834,28 @@
         <v>4.78</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45449.55208333334</v>
+        <v>45450.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>3333</v>
+        <v>3392.35</v>
       </c>
       <c r="I35" t="n">
         <v>3377.645799498549</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K35" t="n">
-        <v>-1.12</v>
+        <v>-2.92</v>
       </c>
       <c r="L35" t="n">
-        <v>2.09</v>
+        <v>2.97</v>
       </c>
       <c r="M35" t="n">
         <v>1.82</v>
       </c>
       <c r="N35" t="n">
-        <v>1.66</v>
+        <v>3.05</v>
       </c>
       <c r="O35" t="n">
         <v>-2.61</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>7.76</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45462.55208333334</v>
+        <v>45463.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>3459</v>
+        <v>3434.3</v>
       </c>
       <c r="I36" t="n">
         <v>3434.385183531268</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K36" t="n">
-        <v>1.96</v>
+        <v>1.24</v>
       </c>
       <c r="L36" t="n">
         <v>2.89</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>5.68</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45495.55208333334</v>
+        <v>45496.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>3249</v>
+        <v>3452.5</v>
       </c>
       <c r="I37" t="n">
         <v>3291.600950617836</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>32.16666666666666</v>
+        <v>33</v>
       </c>
       <c r="K37" t="n">
-        <v>5.4</v>
+        <v>-0.53</v>
       </c>
       <c r="L37" t="n">
         <v>1.62</v>
@@ -2550,7 +2993,7 @@
         <v>0.63</v>
       </c>
       <c r="N37" t="n">
-        <v>1.71</v>
+        <v>6.74</v>
       </c>
       <c r="O37" t="n">
         <v>-0.49</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>7.69</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45511.55208333334</v>
+        <v>45512.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>3330</v>
+        <v>3300.15</v>
       </c>
       <c r="I38" t="n">
         <v>3318.212711231967</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K38" t="n">
-        <v>-3.55</v>
+        <v>-4.41</v>
       </c>
       <c r="L38" t="n">
         <v>6.38</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>5.73</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45520.55208333334</v>
+        <v>45523.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>3447</v>
+        <v>3467.75</v>
       </c>
       <c r="I39" t="n">
         <v>3451.162356436105</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>11</v>
       </c>
       <c r="K39" t="n">
-        <v>-4.45</v>
+        <v>-5.08</v>
       </c>
       <c r="L39" t="n">
-        <v>4.54</v>
+        <v>6.18</v>
       </c>
       <c r="M39" t="n">
         <v>1.77</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,28 +3179,28 @@
         <v>4.22</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45566.55208333334</v>
+        <v>45568.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>3782.95</v>
+        <v>3682.05</v>
       </c>
       <c r="I40" t="n">
         <v>3685.033512371789</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>43.16666666666666</v>
+        <v>45</v>
       </c>
       <c r="K40" t="n">
-        <v>9.09</v>
+        <v>6.18</v>
       </c>
       <c r="L40" t="n">
         <v>0.91</v>
       </c>
       <c r="M40" t="n">
-        <v>0.9399999999999999</v>
+        <v>2.48</v>
       </c>
       <c r="N40" t="n">
-        <v>1.87</v>
+        <v>2.6</v>
       </c>
       <c r="O40" t="n">
         <v>0.47</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>3</v>
+      </c>
+      <c r="U40" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>6.04</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45618.38541666666</v>
+        <v>45618.55208333334</v>
       </c>
       <c r="H41" t="n">
-        <v>3254.05</v>
+        <v>3302</v>
       </c>
       <c r="I41" t="n">
         <v>3294.225525888889</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>50</v>
+        <v>50.16666666666666</v>
       </c>
       <c r="K41" t="n">
-        <v>11.62</v>
+        <v>10.32</v>
       </c>
       <c r="L41" t="n">
         <v>2.71</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>6.11</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45650.55208333334</v>
+        <v>45652.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>3359</v>
+        <v>3342.85</v>
       </c>
       <c r="I42" t="n">
         <v>3344.174101722312</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>32</v>
+        <v>33.83333333333334</v>
       </c>
       <c r="K42" t="n">
-        <v>1.73</v>
+        <v>1.24</v>
       </c>
       <c r="L42" t="n">
         <v>3.08</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>4.34</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45659.38541666666</v>
+        <v>45659.55208333334</v>
       </c>
       <c r="H43" t="n">
-        <v>3337.95</v>
+        <v>3396.95</v>
       </c>
       <c r="I43" t="n">
         <v>3365.116835250356</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>7</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="K43" t="n">
-        <v>0.15</v>
+        <v>-1.62</v>
       </c>
       <c r="L43" t="n">
-        <v>0.87</v>
+        <v>1.74</v>
       </c>
       <c r="M43" t="n">
         <v>0.31</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2928,22 +3455,22 @@
         <v>4.77</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45670.55208333334</v>
+        <v>45671.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>3384.55</v>
+        <v>3333.65</v>
       </c>
       <c r="I44" t="n">
         <v>3365.342228460569</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>11</v>
+        <v>11.83333333333333</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.37</v>
+        <v>-1.86</v>
       </c>
       <c r="L44" t="n">
-        <v>1.81</v>
+        <v>2.14</v>
       </c>
       <c r="M44" t="n">
         <v>1.71</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,28 +3524,28 @@
         <v>6.82</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45687.55208333334</v>
+        <v>45688.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>3371.65</v>
+        <v>3517</v>
       </c>
       <c r="I45" t="n">
         <v>3464.421112217681</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K45" t="n">
-        <v>-1.14</v>
+        <v>-5.5</v>
       </c>
       <c r="L45" t="n">
-        <v>3.42</v>
+        <v>5.67</v>
       </c>
       <c r="M45" t="n">
-        <v>0.48</v>
+        <v>0.84</v>
       </c>
       <c r="N45" t="n">
-        <v>1.32</v>
+        <v>3.55</v>
       </c>
       <c r="O45" t="n">
         <v>-1.46</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,28 +3593,28 @@
         <v>6.61</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45695.55208333334</v>
+        <v>45698.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>3432.85</v>
+        <v>3335.65</v>
       </c>
       <c r="I46" t="n">
         <v>3342.449262630038</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>10</v>
       </c>
       <c r="K46" t="n">
-        <v>-2.39</v>
+        <v>-5.16</v>
       </c>
       <c r="L46" t="n">
-        <v>3.66</v>
+        <v>5.17</v>
       </c>
       <c r="M46" t="n">
-        <v>0.24</v>
+        <v>0.52</v>
       </c>
       <c r="N46" t="n">
-        <v>2.73</v>
+        <v>3.14</v>
       </c>
       <c r="O46" t="n">
         <v>3.55</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3099,28 +3662,28 @@
         <v>8.09</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45735.55208333334</v>
+        <v>45736.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>3077</v>
+        <v>3181.6</v>
       </c>
       <c r="I47" t="n">
         <v>3129.324535359408</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>37.16666666666666</v>
+        <v>38</v>
       </c>
       <c r="K47" t="n">
-        <v>7.75</v>
+        <v>4.62</v>
       </c>
       <c r="L47" t="n">
         <v>2.68</v>
       </c>
       <c r="M47" t="n">
-        <v>0.48</v>
+        <v>0.75</v>
       </c>
       <c r="N47" t="n">
-        <v>2.37</v>
+        <v>3.44</v>
       </c>
       <c r="O47" t="n">
         <v>-3.14</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,22 +3731,22 @@
         <v>5.48</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45740.55208333334</v>
+        <v>45741.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>3076</v>
+        <v>3059.2</v>
       </c>
       <c r="I48" t="n">
         <v>3065.310108420539</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K48" t="n">
-        <v>-3.32</v>
+        <v>-3.85</v>
       </c>
       <c r="L48" t="n">
-        <v>3.35</v>
+        <v>3.98</v>
       </c>
       <c r="M48" t="n">
         <v>0.02</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,28 +3800,28 @@
         <v>4.81</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45748.55208333334</v>
+        <v>45750.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>2988.5</v>
+        <v>3136.4</v>
       </c>
       <c r="I49" t="n">
         <v>3112.354737541324</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>9</v>
       </c>
       <c r="K49" t="n">
-        <v>2.31</v>
+        <v>-2.52</v>
       </c>
       <c r="L49" t="n">
-        <v>1.72</v>
+        <v>3</v>
       </c>
       <c r="M49" t="n">
-        <v>0.68</v>
+        <v>2.76</v>
       </c>
       <c r="N49" t="n">
-        <v>0.62</v>
+        <v>4.57</v>
       </c>
       <c r="O49" t="n">
         <v>-0.9</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>5.92</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45820.38541666666</v>
+        <v>45820.55208333334</v>
       </c>
       <c r="H50" t="n">
-        <v>3512</v>
+        <v>3448.9</v>
       </c>
       <c r="I50" t="n">
         <v>3484.938542342012</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>70</v>
+        <v>70.16666666666667</v>
       </c>
       <c r="K50" t="n">
-        <v>11.98</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="L50" t="n">
         <v>6.74</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>93</v>
+        <v>94</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>3</v>
+      </c>
+      <c r="U50" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -3327,22 +3938,22 @@
         <v>4.57</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45827.55208333334</v>
+        <v>45828.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>3500</v>
+        <v>3536.9</v>
       </c>
       <c r="I51" t="n">
         <v>3527.750911883559</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K51" t="n">
-        <v>-1.48</v>
+        <v>-2.55</v>
       </c>
       <c r="L51" t="n">
-        <v>2.11</v>
+        <v>2.55</v>
       </c>
       <c r="M51" t="n">
         <v>0</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3384,28 +4007,28 @@
         <v>4.25</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45845.55208333334</v>
+        <v>45846.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>3670</v>
+        <v>3461.7</v>
       </c>
       <c r="I52" t="n">
         <v>3590.215943800262</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K52" t="n">
-        <v>3.76</v>
+        <v>-2.13</v>
       </c>
       <c r="L52" t="n">
-        <v>1.81</v>
+        <v>2.29</v>
       </c>
       <c r="M52" t="n">
-        <v>0.86</v>
+        <v>2.4</v>
       </c>
       <c r="N52" t="n">
-        <v>0.7</v>
+        <v>6.25</v>
       </c>
       <c r="O52" t="n">
         <v>0.3</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>6.17</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45873.55208333334</v>
+        <v>45874.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>3350.3</v>
+        <v>3435</v>
       </c>
       <c r="I53" t="n">
         <v>3432.754908593346</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K53" t="n">
-        <v>3.22</v>
+        <v>0.77</v>
       </c>
       <c r="L53" t="n">
         <v>3.47</v>
@@ -3462,7 +4097,7 @@
         <v>0.55</v>
       </c>
       <c r="N53" t="n">
-        <v>1.22</v>
+        <v>2.2</v>
       </c>
       <c r="O53" t="n">
         <v>-6.25</v>
@@ -3471,7 +4106,19 @@
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>4.75</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45911.38541666666</v>
+        <v>45911.55208333334</v>
       </c>
       <c r="H54" t="n">
-        <v>3587.8</v>
+        <v>3580</v>
       </c>
       <c r="I54" t="n">
         <v>3580.016039788543</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>37</v>
+        <v>37.16666666666666</v>
       </c>
       <c r="K54" t="n">
-        <v>4.45</v>
+        <v>4.22</v>
       </c>
       <c r="L54" t="n">
         <v>2.53</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,28 +4214,28 @@
         <v>3.35</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45937.55208333334</v>
+        <v>45938.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>3411.1</v>
+        <v>3573.9</v>
       </c>
       <c r="I55" t="n">
         <v>3468.713198416254</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>26</v>
+        <v>26.83333333333333</v>
       </c>
       <c r="K55" t="n">
-        <v>4.72</v>
+        <v>0.17</v>
       </c>
       <c r="L55" t="n">
         <v>0.6</v>
       </c>
       <c r="M55" t="n">
-        <v>1.02</v>
+        <v>1.84</v>
       </c>
       <c r="N55" t="n">
-        <v>2.53</v>
+        <v>4.57</v>
       </c>
       <c r="O55" t="n">
         <v>-1.1</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>6.15</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45994.55208333334</v>
+        <v>45995.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>3820</v>
+        <v>3796</v>
       </c>
       <c r="I56" t="n">
         <v>3808.073452859593</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>56.16666666666666</v>
+        <v>57</v>
       </c>
       <c r="K56" t="n">
-        <v>6.89</v>
+        <v>6.21</v>
       </c>
       <c r="L56" t="n">
         <v>3.19</v>
@@ -3642,7 +4313,19 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>3</v>
+      </c>
+      <c r="U56" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -3669,22 +4352,22 @@
         <v>3.5</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46006.55208333334</v>
+        <v>46007.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>3856.5</v>
+        <v>3908</v>
       </c>
       <c r="I57" t="n">
         <v>3900.201914646934</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K57" t="n">
-        <v>-1.59</v>
+        <v>-2.95</v>
       </c>
       <c r="L57" t="n">
-        <v>2.6</v>
+        <v>3.21</v>
       </c>
       <c r="M57" t="n">
         <v>0.39</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S57" t="b">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>4.19</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46041.55208333334</v>
+        <v>46042.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>4140</v>
+        <v>4100.9</v>
       </c>
       <c r="I58" t="n">
         <v>4126.54339657063</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>34.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K58" t="n">
-        <v>5.94</v>
+        <v>4.94</v>
       </c>
       <c r="L58" t="n">
         <v>2.05</v>
@@ -3747,7 +4442,7 @@
         <v>0.68</v>
       </c>
       <c r="N58" t="n">
-        <v>1.3</v>
+        <v>1.69</v>
       </c>
       <c r="O58" t="n">
         <v>1.91</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -3783,28 +4490,28 @@
         <v>4.16</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46055.55208333334</v>
+        <v>46056.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>3961.8</v>
+        <v>4090</v>
       </c>
       <c r="I59" t="n">
         <v>4088.300025574598</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K59" t="n">
-        <v>3.39</v>
+        <v>0.27</v>
       </c>
       <c r="L59" t="n">
         <v>1.32</v>
       </c>
       <c r="M59" t="n">
-        <v>1.42</v>
+        <v>4.57</v>
       </c>
       <c r="N59" t="n">
-        <v>0.93</v>
+        <v>2.99</v>
       </c>
       <c r="O59" t="n">
         <v>-1.69</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,25 +4559,25 @@
         <v>6.88</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46083.55208333334</v>
+        <v>46085.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>4258.5</v>
+        <v>4190.7</v>
       </c>
       <c r="I60" t="n">
         <v>4203.495704204903</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K60" t="n">
-        <v>4.12</v>
+        <v>2.46</v>
       </c>
       <c r="L60" t="n">
         <v>1.12</v>
       </c>
       <c r="M60" t="n">
-        <v>1.02</v>
+        <v>1.26</v>
       </c>
       <c r="N60" t="n">
         <v>2.16</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>3.88</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46114.55208333334</v>
+        <v>46118.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>4080</v>
+        <v>4242.3</v>
       </c>
       <c r="I61" t="n">
         <v>4133.721803297801</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>33</v>
       </c>
       <c r="K61" t="n">
-        <v>2.64</v>
+        <v>-1.23</v>
       </c>
       <c r="L61" t="n">
         <v>2.67</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,22 +4697,22 @@
         <v>8.789999999999999</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46154.38541666666</v>
+        <v>46154.55208333334</v>
       </c>
       <c r="H62" t="n">
-        <v>4118.2</v>
+        <v>4058.4</v>
       </c>
       <c r="I62" t="n">
         <v>4117.040886912834</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>36</v>
+        <v>36.16666666666666</v>
       </c>
       <c r="K62" t="n">
-        <v>-2.93</v>
+        <v>-4.33</v>
       </c>
       <c r="L62" t="n">
-        <v>3.24</v>
+        <v>4.6</v>
       </c>
       <c r="M62" t="n">
         <v>3.69</v>
@@ -3984,7 +4727,19 @@
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4011,22 +4766,22 @@
         <v>9.289999999999999</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46177.38541666666</v>
+        <v>46177.55208333334</v>
       </c>
       <c r="H63" t="n">
-        <v>4177.3</v>
+        <v>4250</v>
       </c>
       <c r="I63" t="n">
         <v>4186.75405524803</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>22.83333333333333</v>
+        <v>23</v>
       </c>
       <c r="K63" t="n">
-        <v>-2.93</v>
+        <v>-4.72</v>
       </c>
       <c r="L63" t="n">
-        <v>3.34</v>
+        <v>5.31</v>
       </c>
       <c r="M63" t="n">
         <v>0.88</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,22 +4835,22 @@
         <v>5.69</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46183.38541666666</v>
+        <v>46183.55208333334</v>
       </c>
       <c r="H64" t="n">
-        <v>4076</v>
+        <v>4040</v>
       </c>
       <c r="I64" t="n">
         <v>4043.861234027438</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>5.833333333333333</v>
+        <v>6</v>
       </c>
       <c r="K64" t="n">
-        <v>-4.09</v>
+        <v>-4.94</v>
       </c>
       <c r="L64" t="n">
-        <v>4.28</v>
+        <v>5.06</v>
       </c>
       <c r="M64" t="n">
         <v>1.6</v>
@@ -4098,7 +4865,19 @@
         <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S64" t="b">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -4125,25 +4904,25 @@
         <v>5.26</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46185.55208333334</v>
+        <v>46188.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>4179</v>
+        <v>4273.3</v>
       </c>
       <c r="I65" t="n">
         <v>4224.588882039502</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>2</v>
+        <v>4.833333333333333</v>
       </c>
       <c r="K65" t="n">
-        <v>-3.44</v>
+        <v>-5.77</v>
       </c>
       <c r="L65" t="n">
-        <v>3.96</v>
+        <v>6.18</v>
       </c>
       <c r="M65" t="n">
-        <v>0.91</v>
+        <v>1.01</v>
       </c>
       <c r="N65" t="n">
         <v>3.67</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S65" t="b">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>5.76</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46267.55208333334</v>
+        <v>46268.38541666666</v>
       </c>
       <c r="H66" t="n">
-        <v>5055</v>
+        <v>4998.5</v>
       </c>
       <c r="I66" t="n">
         <v>5016.0760012006</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>79.16666666666667</v>
+        <v>80</v>
       </c>
       <c r="K66" t="n">
-        <v>18.29</v>
+        <v>16.97</v>
       </c>
       <c r="L66" t="n">
         <v>1.24</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>114</v>
+        <v>115</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>4</v>
+      </c>
+      <c r="U66" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="67">
@@ -4263,6 +5066,14 @@
       <c r="Q67" t="n">
         <v>74</v>
       </c>
+      <c r="R67" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="inlineStr"/>
+      <c r="U67" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6365,7 +7176,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25.1</v>
+        <v>26.1</v>
       </c>
     </row>
     <row r="6">
@@ -6375,7 +7186,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18.2</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7">
@@ -6385,7 +7196,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>88.2</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8">
@@ -6395,7 +7206,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="9">
@@ -6405,7 +7216,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>33.2</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10">
@@ -6415,7 +7226,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>51.8</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11">
@@ -6425,7 +7236,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12">
@@ -6435,7 +7246,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13">
@@ -6445,7 +7256,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>69.2</v>
+        <v>67.7</v>
       </c>
     </row>
     <row r="14">
@@ -6455,7 +7266,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.62</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="15">
@@ -6465,7 +7276,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.52</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="16">
@@ -6475,7 +7286,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.69</v>
+        <v>-0.68</v>
       </c>
     </row>
     <row r="17">
@@ -6485,7 +7296,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>29.35</v>
+        <v>28.82</v>
       </c>
     </row>
     <row r="18">
@@ -6495,7 +7306,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>60</v>
+        <v>35.4</v>
       </c>
     </row>
     <row r="19">
@@ -6505,7 +7316,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.85</v>
+        <v>3.44</v>
       </c>
     </row>
     <row r="20">
@@ -6515,7 +7326,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.7</v>
+        <v>3.18</v>
       </c>
     </row>
     <row r="21">
@@ -6525,7 +7336,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>6.74</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -6535,7 +7346,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23">
@@ -6555,7 +7366,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.19</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="25">
@@ -6575,7 +7386,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.27</v>
+        <v>3.02</v>
       </c>
     </row>
     <row r="27">
@@ -6595,7 +7406,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="29">
